--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488159_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488159_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.5926</v>
+        <v>7.5758</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0721</v>
+        <v>3.0156</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5205</v>
+        <v>4.5602</v>
       </c>
       <c r="G2" t="n">
         <v>5.1032</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3052</v>
+        <v>2.2884</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0417</v>
+        <v>0.9852</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2634</v>
+        <v>1.3032</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0011</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1326</v>
+        <v>7.5752</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6609</v>
+        <v>4.7588</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4717</v>
+        <v>2.8164</v>
       </c>
       <c r="G3" t="n">
         <v>3.5905</v>
@@ -688,13 +688,13 @@
         <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2298</v>
+        <v>0.6724</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1679</v>
+        <v>-0.0699</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3977</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>5.3504</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5985</v>
+        <v>4.8124</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3263</v>
+        <v>2.7684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2722</v>
+        <v>2.044</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5305</v>
+        <v>7.2088</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3063</v>
+        <v>0.885</v>
       </c>
       <c r="I4" t="n">
-        <v>2.2242</v>
+        <v>6.3237</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7968</v>
+        <v>5.4093</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7647</v>
+        <v>0.2147</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0321</v>
+        <v>5.1946</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2663</v>
+        <v>1.7995</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4584</v>
+        <v>0.6703</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1922</v>
+        <v>1.1292</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>0.383</v>
+        <v>0.53</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2151</v>
+        <v>0.1384</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1679</v>
+        <v>0.3917</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.25</v>
+        <v>4.4027</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0829</v>
+        <v>4.1305</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1671</v>
+        <v>0.2722</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2088</v>
+        <v>3.5305</v>
       </c>
       <c r="H5" t="n">
-        <v>0.885</v>
+        <v>1.3063</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3237</v>
+        <v>2.2242</v>
       </c>
       <c r="J5" t="n">
-        <v>5.4093</v>
+        <v>3.7968</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2147</v>
+        <v>1.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1946</v>
+        <v>2.0321</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7995</v>
+        <v>-0.2663</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6703</v>
+        <v>-0.4584</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1292</v>
+        <v>0.1922</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0324</v>
+        <v>0.1871</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5471</v>
+        <v>0.0193</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5148</v>
+        <v>0.1679</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>U. FRISCIA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.966</v>
+        <v>1.8905</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0616</v>
+        <v>-1.0585</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9044</v>
+        <v>2.9491</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8496</v>
+        <v>1.3465</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2379</v>
+        <v>0.8119</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0875</v>
+        <v>0.5346</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7729</v>
+        <v>-0.3367</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5542</v>
+        <v>0.1503</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3271</v>
+        <v>-0.487</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0767</v>
+        <v>1.6832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3163</v>
+        <v>0.6616</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7604</v>
+        <v>1.0216</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6722</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2151</v>
+        <v>0.2046</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4571</v>
+        <v>0.5248</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3591</v>
+        <v>1.4998</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4348</v>
+        <v>-0.2322</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7939</v>
+        <v>1.7321</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6461</v>
+        <v>1.8496</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5832000000000001</v>
+        <v>-0.2379</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0629</v>
+        <v>2.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2029</v>
+        <v>0.7729</v>
       </c>
       <c r="K7" t="n">
         <v>-0.5542</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7572</v>
+        <v>1.3271</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4432</v>
+        <v>1.0767</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1374</v>
+        <v>0.3163</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3057</v>
+        <v>0.7604</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.5558999999999999</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2688</v>
+        <v>0.2061</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2151</v>
+        <v>-0.0786</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0537</v>
+        <v>0.2848</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. FRISCIA PEREZ</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0814</v>
+        <v>1.2858</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6461</v>
+        <v>-1.5327</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7275</v>
+        <v>2.8185</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3465</v>
+        <v>2.6461</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8119</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5346</v>
+        <v>2.0629</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3367</v>
+        <v>0.2029</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1503</v>
+        <v>-0.5542</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.487</v>
+        <v>0.7572</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6832</v>
+        <v>2.4432</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6616</v>
+        <v>1.1374</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0216</v>
+        <v>1.3057</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0798</v>
+        <v>0.1955</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.383</v>
+        <v>0.1172</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3032</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>J. ILLANES TENLLADO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0885</v>
+        <v>0.0149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.422</v>
+        <v>-1.0284</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5105</v>
+        <v>1.0433</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4187</v>
+        <v>-0.1787</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0592</v>
+        <v>0.213</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3595</v>
+        <v>-0.3917</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6408</v>
+        <v>-0.9622000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4335</v>
+        <v>-0.3093</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2074</v>
+        <v>-0.6529</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7779</v>
+        <v>0.7834</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3743</v>
+        <v>0.5223</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1522</v>
+        <v>0.2611</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2189</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2288</v>
+        <v>0.0746</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. ILLANES TENLLADO</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2061</v>
+        <v>-0.1137</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1263</v>
+        <v>0.5199</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9202</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1787</v>
+        <v>1.4187</v>
       </c>
       <c r="H10" t="n">
-        <v>0.213</v>
+        <v>0.0592</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3917</v>
+        <v>1.3595</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9622000000000001</v>
+        <v>0.6408</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3093</v>
+        <v>0.4335</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6529</v>
+        <v>0.2074</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7834</v>
+        <v>0.7779</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5223</v>
+        <v>-0.3743</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2611</v>
+        <v>1.1522</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2126</v>
+        <v>-0.0152</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1641</v>
+        <v>-0.1209</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0485</v>
+        <v>0.1057</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. SECK DIOP</t>
+          <t>P. VILLAREJO CALATAYUD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6017</v>
+        <v>-0.1568</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7834</v>
+        <v>-2.5881</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1817</v>
+        <v>2.4314</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1435</v>
+        <v>1.3479</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7103</v>
+        <v>-0.0145</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4332</v>
+        <v>1.3624</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0506</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0092</v>
+        <v>-0.7689</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0415</v>
+        <v>0.7785</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0929</v>
+        <v>1.3383</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2989</v>
+        <v>0.7544</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3917</v>
+        <v>0.5839</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.594</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q11" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2189</v>
+        <v>0.3482</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0547</v>
+        <v>0.1816</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2736</v>
+        <v>0.1666</v>
       </c>
       <c r="V11" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. VILLAREJO CALATAYUD</t>
+          <t>K. SECK DIOP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2603</v>
+        <v>-0.6017</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3716</v>
+        <v>-1.7834</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1113</v>
+        <v>1.1817</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3479</v>
+        <v>1.1435</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0145</v>
+        <v>0.7103</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3624</v>
+        <v>0.4332</v>
       </c>
       <c r="J12" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.0506</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7689</v>
+        <v>1.0092</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7785</v>
+        <v>0.0415</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3383</v>
+        <v>0.0929</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7544</v>
+        <v>-0.2989</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5839</v>
+        <v>0.3917</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8529</v>
+        <v>-2.594</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9264</v>
+        <v>0.1853</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7553</v>
+        <v>0.2189</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6019</v>
+        <v>-0.0547</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1535</v>
+        <v>0.2736</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4021</v>
+        <v>-1.7636</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1837</v>
+        <v>-1.8899</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2185</v>
+        <v>0.1262</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1722</v>
@@ -1468,13 +1468,13 @@
         <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9155</v>
+        <v>-0.277</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4924</v>
+        <v>-0.1986</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4231</v>
+        <v>-0.0784</v>
       </c>
       <c r="V13" t="n">
         <v>0.315</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.4215</v>
+        <v>26.4213</v>
       </c>
       <c r="E14" t="n">
-        <v>5.079900000000001</v>
+        <v>5.079999999999999</v>
       </c>
       <c r="F14" t="n">
         <v>21.3415</v>
@@ -1513,7 +1513,7 @@
         <v>26.8344</v>
       </c>
       <c r="H14" t="n">
-        <v>9.285099999999998</v>
+        <v>9.2851</v>
       </c>
       <c r="I14" t="n">
         <v>17.5492</v>
@@ -1531,7 +1531,7 @@
         <v>11.466</v>
       </c>
       <c r="N14" t="n">
-        <v>2.785699999999999</v>
+        <v>2.7857</v>
       </c>
       <c r="O14" t="n">
         <v>8.680300000000001</v>
@@ -1546,13 +1546,13 @@
         <v>7.411399999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>5.0922</v>
+        <v>5.092099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.057</v>
+        <v>1.0574</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0351</v>
+        <v>4.0352</v>
       </c>
       <c r="V14" t="n">
         <v>2.8327</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4607</v>
+        <v>3.191</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8943</v>
+        <v>4.6985</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4336</v>
+        <v>-1.5075</v>
       </c>
       <c r="G15" t="n">
         <v>0.8466</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3176</v>
+        <v>0.0479</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2114</v>
+        <v>0.0156</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1062</v>
+        <v>0.0323</v>
       </c>
       <c r="V15" t="n">
         <v>0.6289</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-1.1834</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8549</v>
+        <v>-2.4425</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2344</v>
+        <v>1.259</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5579</v>
@@ -1780,13 +1780,13 @@
         <v>1.1117</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3074</v>
+        <v>-0.2555</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5397</v>
+        <v>-0.0479</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2323</v>
+        <v>-0.2077</v>
       </c>
       <c r="V17" t="n">
         <v>0.63</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1763</v>
+        <v>-1.2606</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6019</v>
+        <v>-2.3254</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5744</v>
+        <v>1.0647</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.7803</v>
+        <v>-1.1755</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3935</v>
+        <v>-0.7608</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3869</v>
+        <v>-0.4147</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6492</v>
+        <v>-0.6099</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5321</v>
+        <v>0.0429</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1813</v>
+        <v>-0.6529</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1311</v>
+        <v>-0.5656</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9255</v>
+        <v>-0.8037</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2056</v>
+        <v>0.2381</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5653</v>
+        <v>-0.4558</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0473</v>
+        <v>-0.789</v>
       </c>
       <c r="U18" t="n">
-        <v>0.518</v>
+        <v>0.3333</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2349</v>
+        <v>-1.6346</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5212</v>
+        <v>-1.1151</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2863</v>
+        <v>-0.5195</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1755</v>
+        <v>-1.4337</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7608</v>
+        <v>-0.7225</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4147</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6099</v>
+        <v>0.1006</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0429</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6529</v>
+        <v>0.0107</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5656</v>
+        <v>-1.5343</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8037</v>
+        <v>-0.8124</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2381</v>
+        <v>-0.7219</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.43</v>
+        <v>-0.0892</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9849</v>
+        <v>0.0078</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5548</v>
+        <v>-0.097</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6352</v>
+        <v>-1.6676</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0171</v>
+        <v>-0.7978</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.618</v>
+        <v>-0.8698</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4337</v>
+        <v>-2.7803</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7225</v>
+        <v>-0.3935</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-2.3869</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1006</v>
+        <v>-0.6492</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.5321</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0107</v>
+        <v>-1.1813</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5343</v>
+        <v>-2.1311</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8124</v>
+        <v>-0.9255</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7219</v>
+        <v>-1.2056</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>1.6676</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0898</v>
+        <v>0.074</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1057</v>
+        <v>-0.1486</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1955</v>
+        <v>0.2226</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6294</v>
+        <v>-0.6289</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6068</v>
+        <v>-2.3371</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8423</v>
+        <v>-1.6464</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7645999999999999</v>
+        <v>-0.6907</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1614</v>
@@ -2092,13 +2092,13 @@
         <v>1.4823</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0749</v>
+        <v>-0.8052</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8754</v>
+        <v>-0.6796</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1995</v>
+        <v>-0.1256</v>
       </c>
       <c r="V21" t="n">
         <v>1.2589</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>F. GERONIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9483</v>
+        <v>-2.9566</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.1284</v>
+        <v>-3.3369</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1801</v>
+        <v>0.3803</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6684</v>
+        <v>-2.0155</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5563</v>
+        <v>-1.3811</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1121</v>
+        <v>-0.6344</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.57</v>
+        <v>-1.9171</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.6114</v>
+        <v>-1.3057</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0415</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-0.0984</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0552</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1536</v>
+        <v>-0.023</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1853</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0766</v>
+        <v>-0.7558</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1131</v>
+        <v>-0.3081</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0365</v>
+        <v>-0.4477</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. GERONIN</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3735</v>
+        <v>-3.3411</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6307</v>
+        <v>-4.3242</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2572</v>
+        <v>0.9831</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0155</v>
+        <v>-2.6684</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3811</v>
+        <v>-2.5563</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6344</v>
+        <v>-0.1121</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9171</v>
+        <v>-2.57</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3057</v>
+        <v>-2.6114</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0415</v>
       </c>
       <c r="M23" t="n">
         <v>-0.0984</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.0552</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.023</v>
+        <v>-0.1536</v>
       </c>
       <c r="P23" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-0.1853</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-1.1117</v>
       </c>
       <c r="R23" t="n">
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1727</v>
+        <v>-0.4694</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6019</v>
+        <v>-0.309</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5708</v>
+        <v>-0.1604</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.9444</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1269</v>
+        <v>-3.5393</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4639</v>
+        <v>-1.8763</v>
       </c>
       <c r="F24" t="n">
         <v>-1.663</v>
@@ -2326,10 +2326,10 @@
         <v>1.4823</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0359</v>
+        <v>-0.4483</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2037</v>
+        <v>-0.6162</v>
       </c>
       <c r="U24" t="n">
         <v>0.1679</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1765</v>
+        <v>-4.4692</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4333</v>
+        <v>-1.9229</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.7432</v>
+        <v>-2.5462</v>
       </c>
       <c r="G25" t="n">
         <v>-3.7954</v>
@@ -2404,13 +2404,13 @@
         <v>1.6676</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4743</v>
+        <v>-0.7669</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0473</v>
+        <v>-0.4424</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5215</v>
+        <v>-0.3246</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5744</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.6053</v>
+        <v>-7.8448</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.3642</v>
+        <v>-6.8745</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2411</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-8.456099999999999</v>
@@ -2482,13 +2482,13 @@
         <v>2.4087</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9285</v>
+        <v>-1.168</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.2074</v>
+        <v>-0.7178</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.721</v>
+        <v>-0.4502</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6294</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-26.4214</v>
+        <v>-26.4212</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.3415</v>
+        <v>-21.3414</v>
       </c>
       <c r="F27" t="n">
         <v>-5.0799</v>
@@ -2548,7 +2548,7 @@
         <v>-6.499</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.869399999999999</v>
+        <v>-8.869400000000001</v>
       </c>
       <c r="P27" t="n">
         <v>8.337999999999999</v>
@@ -2560,13 +2560,13 @@
         <v>15.7493</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.0924</v>
+        <v>-5.0922</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.035</v>
+        <v>-4.035200000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.0572</v>
+        <v>-1.0571</v>
       </c>
       <c r="V27" t="n">
         <v>-2.8326</v>
